--- a/data/ams_weekly_data/Nexlev/ads_report_week16.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week16.xlsx
@@ -7679,7 +7679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7936,23 +7936,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4858</v>
+        <v>14574</v>
       </c>
       <c r="E8" t="n">
-        <v>86.33333333333333</v>
+        <v>259</v>
       </c>
       <c r="F8" t="n">
-        <v>3207.24</v>
+        <v>9621.719999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>5748.87</v>
+        <v>17246.61</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -7964,28 +7964,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nex_HnK_SBV_KT_SC-05_B0F43P6D23_BCG_Phrase &amp; Exact_Reel</t>
+          <t>Nex_HnK_SB_KT_GS-02/05_B0CDPMX152_B0D383WQPB</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4858</v>
+        <v>32227</v>
       </c>
       <c r="E9" t="n">
-        <v>86.33333333333333</v>
+        <v>51</v>
       </c>
       <c r="F9" t="n">
-        <v>3207.24</v>
+        <v>1070.61</v>
       </c>
       <c r="G9" t="n">
-        <v>5748.87</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -7997,28 +7997,28 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nex_HnK_SBV_KT_SC-05_B0F43P6D23_BCG_Phrase &amp; Exact_Reel</t>
+          <t>Nex_HnK_SB_KT_GS-02/05_B0CDPMX152_B0D383WQPB</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4858</v>
+        <v>32227</v>
       </c>
       <c r="E10" t="n">
-        <v>86.33333333333333</v>
+        <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>3207.24</v>
+        <v>1070.61</v>
       </c>
       <c r="G10" t="n">
-        <v>5748.87</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -8035,14 +8035,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>32227</v>
       </c>
       <c r="E11" t="n">
-        <v>50.66666666666666</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
         <v>1070.61</v>
@@ -8063,22 +8063,22 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_GS-02/05_B0CDPMX152_B0D383WQPB</t>
+          <t>Nex_Hnk_SBV_KT_ST-01_B0DVC7VJP1_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>32227</v>
+        <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>50.66666666666666</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>1070.61</v>
+        <v>52.67</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -8096,28 +8096,28 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_GS-02/05_B0CDPMX152_B0D383WQPB</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>32227</v>
+        <v>47000</v>
       </c>
       <c r="E13" t="n">
-        <v>50.66666666666666</v>
+        <v>484</v>
       </c>
       <c r="F13" t="n">
-        <v>1070.61</v>
+        <v>10528.78314018273</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>46151.34266437748</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -8129,28 +8129,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SBV_KT_ST-01_B0DVC7VJP1_Phrase &amp; Exact</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>28</v>
+        <v>17824</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>179</v>
       </c>
       <c r="F14" t="n">
-        <v>52.67</v>
+        <v>3895.204615107282</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>16443.15380184249</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -8167,23 +8167,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>30314.66666666667</v>
+        <v>25728</v>
       </c>
       <c r="E15" t="n">
-        <v>308.3333333333333</v>
+        <v>258</v>
       </c>
       <c r="F15" t="n">
-        <v>6710.836666666667</v>
+        <v>5622.725591013498</v>
       </c>
       <c r="G15" t="n">
-        <v>28897.45333333333</v>
+        <v>23735.68292664499</v>
       </c>
       <c r="H15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -8200,23 +8200,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>30314.66666666667</v>
+        <v>393</v>
       </c>
       <c r="E16" t="n">
-        <v>308.3333333333333</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>6710.836666666667</v>
+        <v>85.79665369648808</v>
       </c>
       <c r="G16" t="n">
-        <v>28897.45333333333</v>
+        <v>362.1806071350417</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -8228,28 +8228,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>30314.66666666667</v>
+        <v>747</v>
       </c>
       <c r="E17" t="n">
-        <v>308.3333333333333</v>
+        <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>6710.836666666667</v>
+        <v>298.1666565831778</v>
       </c>
       <c r="G17" t="n">
-        <v>28897.45333333333</v>
+        <v>1205.955784789168</v>
       </c>
       <c r="H17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -8266,23 +8266,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6099</v>
+        <v>1804</v>
       </c>
       <c r="E18" t="n">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="F18" t="n">
-        <v>2435.855</v>
+        <v>720.4132505901073</v>
       </c>
       <c r="G18" t="n">
-        <v>9851.985000000001</v>
+        <v>2913.761508224003</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -8299,23 +8299,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6099</v>
+        <v>6307</v>
       </c>
       <c r="E19" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F19" t="n">
-        <v>2435.855</v>
+        <v>2518.805406700359</v>
       </c>
       <c r="G19" t="n">
-        <v>9851.985000000001</v>
+        <v>10187.48369042116</v>
       </c>
       <c r="H19" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -8327,28 +8327,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
+          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2111</v>
+        <v>3341</v>
       </c>
       <c r="E20" t="n">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="F20" t="n">
-        <v>660.215</v>
+        <v>1334.324686126356</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>5396.76901656567</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -8393,28 +8393,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>31414</v>
+        <v>2111</v>
       </c>
       <c r="E22" t="n">
-        <v>691</v>
+        <v>52</v>
       </c>
       <c r="F22" t="n">
-        <v>10690.21</v>
+        <v>660.215</v>
       </c>
       <c r="G22" t="n">
-        <v>47435.57</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -8426,28 +8426,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1849.5</v>
+        <v>23698</v>
       </c>
       <c r="E23" t="n">
-        <v>99.5</v>
+        <v>523</v>
       </c>
       <c r="F23" t="n">
-        <v>586.975</v>
+        <v>8038.901701105578</v>
       </c>
       <c r="G23" t="n">
-        <v>3807.62</v>
+        <v>36425.38016716031</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -8459,28 +8459,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1849.5</v>
+        <v>2164</v>
       </c>
       <c r="E24" t="n">
-        <v>99.5</v>
+        <v>47</v>
       </c>
       <c r="F24" t="n">
-        <v>586.975</v>
+        <v>743.4448251404457</v>
       </c>
       <c r="G24" t="n">
-        <v>3807.62</v>
+        <v>3087.331887601265</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -8492,28 +8492,28 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15552</v>
+        <v>5553</v>
       </c>
       <c r="E25" t="n">
-        <v>688</v>
+        <v>121</v>
       </c>
       <c r="F25" t="n">
-        <v>10621.45</v>
+        <v>1907.863473753976</v>
       </c>
       <c r="G25" t="n">
-        <v>31430.51</v>
+        <v>7922.857945238422</v>
       </c>
       <c r="H25" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -8525,28 +8525,28 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>19600</v>
+        <v>3699</v>
       </c>
       <c r="E26" t="n">
-        <v>62</v>
+        <v>199</v>
       </c>
       <c r="F26" t="n">
-        <v>1051.57</v>
+        <v>1173.95</v>
       </c>
       <c r="G26" t="n">
-        <v>2047.46</v>
+        <v>7615.24</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6666666666666666</v>
+        <v>4</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -8558,28 +8558,28 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>19600</v>
+        <v>7632</v>
       </c>
       <c r="E27" t="n">
-        <v>62</v>
+        <v>338</v>
       </c>
       <c r="F27" t="n">
-        <v>1051.57</v>
+        <v>5212.532620562809</v>
       </c>
       <c r="G27" t="n">
-        <v>2047.46</v>
+        <v>15424.68859298171</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6666666666666666</v>
+        <v>6</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -8591,28 +8591,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>19600</v>
+        <v>3147</v>
       </c>
       <c r="E28" t="n">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="F28" t="n">
-        <v>1051.57</v>
+        <v>2149.377758637506</v>
       </c>
       <c r="G28" t="n">
-        <v>2047.46</v>
+        <v>6360.340550172879</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6666666666666666</v>
+        <v>3</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -8624,28 +8624,28 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>41569.5</v>
+        <v>4563</v>
       </c>
       <c r="E29" t="n">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="F29" t="n">
-        <v>563.5700000000001</v>
+        <v>3116.556733462985</v>
       </c>
       <c r="G29" t="n">
-        <v>1270.765</v>
+        <v>9222.372423414474</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -8657,30 +8657,96 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0F678L8YT</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>209</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>142.9828873367</v>
+      </c>
+      <c r="G30" t="n">
+        <v>423.1084334309367</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>58800</v>
+      </c>
+      <c r="E31" t="n">
+        <v>186</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3154.71</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6142.38</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>41569.5</v>
-      </c>
-      <c r="E30" t="n">
-        <v>48</v>
-      </c>
-      <c r="F30" t="n">
-        <v>563.5700000000001</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1270.765</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I30" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>83139</v>
+      </c>
+      <c r="E32" t="n">
+        <v>96</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1127.14</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2541.53</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week16.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week16.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
